--- a/tests/v2/live-api/data/sample-units-import.xlsx
+++ b/tests/v2/live-api/data/sample-units-import.xlsx
@@ -464,7 +464,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VCS-2024-001-BLK-1000-5000</v>
+        <v>SAMPLE-UNIT1-BLK-1000-5000</v>
       </c>
       <c r="B2" t="str">
         <v>1000</v>
@@ -473,7 +473,7 @@
         <v>5000</v>
       </c>
       <c r="D2">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="E2" t="str">
         <v>Removal - nature</v>
@@ -485,28 +485,28 @@
         <v>Issued</v>
       </c>
       <c r="H2" t="str">
-        <v>Initial issuance from first verification period</v>
+        <v>Sample initial issuance from first verification period</v>
       </c>
       <c r="I2" t="str">
         <v>2024-06-15</v>
       </c>
       <c r="M2" t="str">
-        <v>https://registry.verra.org/app/units/VCS/2024001/1000-5000</v>
+        <v>https://example.com/registry/units/sample-unit1-1000-5000</v>
       </c>
       <c r="N2" t="str">
         <v>tCO2e</v>
       </c>
       <c r="O2" t="str">
-        <v>Mekong Delta Conservation Trust</v>
+        <v>Example Conservation Trust</v>
       </c>
       <c r="Q2" t="str">
-        <v>Climate Impact Exchange</v>
+        <v>Example Carbon Exchange</v>
       </c>
       <c r="R2" t="str">
-        <v>https://climateimpact.exchange/units/vcs-2024-001-1</v>
+        <v>https://example.com/exchange/units/sample-unit1-blk1</v>
       </c>
       <c r="S2" t="str">
-        <v>CIX-VCS-2024-001-BLK1</v>
+        <v>SAMPLE-EXC-UNIT1-BLK1</v>
       </c>
       <c r="T2" t="str">
         <v>{{ISSUANCE_ID}}</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>VCS-2024-001-BLK-5001-7000</v>
+        <v>SAMPLE-UNIT2-BLK-5001-7000</v>
       </c>
       <c r="B3" t="str">
         <v>5001</v>
@@ -535,28 +535,28 @@
         <v>Retired</v>
       </c>
       <c r="H3" t="str">
-        <v>Voluntary retirement for corporate carbon neutrality pledge</v>
+        <v>Sample voluntary retirement for corporate sustainability pledge</v>
       </c>
       <c r="I3" t="str">
         <v>2025-01-20</v>
       </c>
       <c r="J3" t="str">
-        <v>Retired on behalf of Acme Corp 2024 sustainability commitment. Credits permanently removed from circulation.</v>
+        <v>Sample retirement on behalf of Example Corporation for testing. Credits permanently removed from circulation.</v>
       </c>
       <c r="K3" t="str">
-        <v>Acme Corporation</v>
+        <v>Example Corporation</v>
       </c>
       <c r="L3" t="str">
-        <v>ACME-2024-CN-001</v>
+        <v>SAMPLE-CORP-2024-001</v>
       </c>
       <c r="M3" t="str">
-        <v>https://registry.verra.org/app/units/VCS/2024001/5001-7000</v>
+        <v>https://example.com/registry/units/sample-unit2-5001-7000</v>
       </c>
       <c r="N3" t="str">
         <v>tCO2e</v>
       </c>
       <c r="O3" t="str">
-        <v>Acme Corporation</v>
+        <v>Example Corporation</v>
       </c>
       <c r="T3" t="str">
         <v>{{ISSUANCE_ID}}</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GS-10542-BLK-1-2500</v>
+        <v>SAMPLE-UNIT3-BLK-1-2500</v>
       </c>
       <c r="B4" t="str">
         <v>1</v>
@@ -585,7 +585,7 @@
         <v>Buffer</v>
       </c>
       <c r="H4" t="str">
-        <v>Allocated to permanence buffer pool per Gold Standard requirements</v>
+        <v>Sample allocation to permanence buffer pool</v>
       </c>
       <c r="I4" t="str">
         <v>2024-09-01</v>
@@ -594,7 +594,7 @@
         <v>tCO2e</v>
       </c>
       <c r="O4" t="str">
-        <v>Gold Standard Foundation Buffer Account</v>
+        <v>Example Buffer Account</v>
       </c>
       <c r="T4" t="str">
         <v>{{ISSUANCE_ID}}</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CAR-2025-078-BLK-1-10000</v>
+        <v>SAMPLE-UNIT4-BLK-1-10000</v>
       </c>
       <c r="B5" t="str">
         <v>1</v>
@@ -623,31 +623,31 @@
         <v>Held</v>
       </c>
       <c r="H5" t="str">
-        <v>Held pending verification of second monitoring period</v>
+        <v>Sample hold pending verification of second monitoring period</v>
       </c>
       <c r="I5" t="str">
         <v>2025-03-01</v>
       </c>
       <c r="M5" t="str">
-        <v>https://www.climateactionreserve.org/units/2025-078/1-10000</v>
+        <v>https://example.com/registry/units/sample-unit4-1-10000</v>
       </c>
       <c r="N5" t="str">
         <v>tCO2e</v>
       </c>
       <c r="O5" t="str">
-        <v>Pacific Northwest Forest Holdings LLC</v>
+        <v>Example Forestry Management Inc</v>
       </c>
       <c r="P5" t="str">
-        <v>ITMOS-US-2025-078-001</v>
+        <v>SAMPLE-ITMOS-2025-001</v>
       </c>
       <c r="Q5" t="str">
-        <v>Xpansiv CBL</v>
+        <v>Example Marketplace</v>
       </c>
       <c r="R5" t="str">
-        <v>https://xpansiv.com/cbl/listings/car-2025-078</v>
+        <v>https://example.com/marketplace/listings/sample-unit4-2025</v>
       </c>
       <c r="S5" t="str">
-        <v>CBL-CAR-2025-078-001</v>
+        <v>SAMPLE-MKT-UNIT4-001</v>
       </c>
       <c r="T5" t="str">
         <v>{{ISSUANCE_ID}}</v>
@@ -683,13 +683,13 @@
         <v>{{LABEL_ID}}</v>
       </c>
       <c r="B2" t="str">
-        <v>NEW-1</v>
+        <v>NEW-3</v>
       </c>
       <c r="C2" t="str">
         <v>2024-06-15</v>
       </c>
       <c r="D2" t="str">
-        <v>Gold Standard Certified — meets all GS4GG requirements for community benefit and environmental integrity</v>
+        <v>Sample certification label — example description for unit testing</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v>2025-03-01</v>
       </c>
       <c r="D3" t="str">
-        <v>Article 6.4 authorized credit — eligible for corresponding adjustment under Paris Agreement framework</v>
+        <v>Sample authorized credit label — example description for unit testing</v>
       </c>
     </row>
   </sheetData>

--- a/tests/v2/live-api/data/sample-units-import.xlsx
+++ b/tests/v2/live-api/data/sample-units-import.xlsx
@@ -398,264 +398,279 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>cadTrustUnitId</v>
+      </c>
+      <c r="B1" t="str">
         <v>unitSerialId</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>unitStartBlock</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>unitEndBlock</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>unitCount</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>unitType</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>unitVintageYear</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>unitStatus</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>unitStatusReason</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>unitStatusDate</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>unitRetirementDetail</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>unitRetirementBeneficiary</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>unitRetirementBeneficiaryId</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>unitLink</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>unitMetric</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>unitCurrentOwner</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>unitItmosReferenceId</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>marketplace</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>marketplaceLink</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>marketplaceIdentifier</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>cadTrustIssuanceId</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>NEW-1</v>
+      </c>
+      <c r="B2" t="str">
         <v>SAMPLE-UNIT1-BLK-1000-5000</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>1000</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>5000</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>4001</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Removal - nature</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>2024</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Issued</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Sample initial issuance from first verification period</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>2024-06-15</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>https://example.com/registry/units/sample-unit1-1000-5000</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>tCO2e</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>Example Conservation Trust</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>Example Carbon Exchange</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>https://example.com/exchange/units/sample-unit1-blk1</v>
       </c>
-      <c r="S2" t="str">
+      <c r="T2" t="str">
         <v>SAMPLE-EXC-UNIT1-BLK1</v>
       </c>
-      <c r="T2" t="str">
+      <c r="U2" t="str">
         <v>{{ISSUANCE_ID}}</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>NEW-2</v>
+      </c>
+      <c r="B3" t="str">
         <v>SAMPLE-UNIT2-BLK-5001-7000</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>5001</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>7000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2000</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Removal - nature</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>2024</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Retired</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Sample voluntary retirement for corporate sustainability pledge</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>2025-01-20</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Sample retirement on behalf of Example Corporation for testing. Credits permanently removed from circulation.</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Example Corporation</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>SAMPLE-CORP-2024-001</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>https://example.com/registry/units/sample-unit2-5001-7000</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>tCO2e</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>Example Corporation</v>
       </c>
-      <c r="T3" t="str">
+      <c r="U3" t="str">
         <v>{{ISSUANCE_ID}}</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>NEW-3</v>
+      </c>
+      <c r="B4" t="str">
         <v>SAMPLE-UNIT3-BLK-1-2500</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>1</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>2500</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>2500</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Avoidance - technical</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>2024</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Buffer</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Sample allocation to permanence buffer pool</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>2024-09-01</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>tCO2e</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>Example Buffer Account</v>
       </c>
-      <c r="T4" t="str">
+      <c r="U4" t="str">
         <v>{{ISSUANCE_ID}}</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>NEW-4</v>
+      </c>
+      <c r="B5" t="str">
         <v>SAMPLE-UNIT4-BLK-1-10000</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>1</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>10000</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>10000</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Removal - nature</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2025</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Held</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Sample hold pending verification of second monitoring period</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>2025-03-01</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>https://example.com/registry/units/sample-unit4-1-10000</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>tCO2e</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>Example Forestry Management Inc</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>SAMPLE-ITMOS-2025-001</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>Example Marketplace</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <v>https://example.com/marketplace/listings/sample-unit4-2025</v>
       </c>
-      <c r="S5" t="str">
+      <c r="T5" t="str">
         <v>SAMPLE-MKT-UNIT4-001</v>
       </c>
-      <c r="T5" t="str">
+      <c r="U5" t="str">
         <v>{{ISSUANCE_ID}}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U5"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tests/v2/live-api/data/sample-units-import.xlsx
+++ b/tests/v2/live-api/data/sample-units-import.xlsx
@@ -677,53 +677,62 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>cadTrustUnitLabelId</v>
+      </c>
+      <c r="B1" t="str">
         <v>cadTrustLabelId</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>cadTrustUnitId</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>labelUnitDate</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>labelUnitDescription</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>NEW-1</v>
+      </c>
+      <c r="B2" t="str">
         <v>{{LABEL_ID}}</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>NEW-3</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>2024-06-15</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Sample certification label — example description for unit testing</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>NEW-2</v>
+      </c>
+      <c r="B3" t="str">
         <v>{{LABEL_ID}}</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>NEW-4</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>2025-03-01</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Sample authorized credit label — example description for unit testing</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tests/v2/live-api/data/sample-units-import.xlsx
+++ b/tests/v2/live-api/data/sample-units-import.xlsx
@@ -698,7 +698,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>NEW-1</v>
+        <v>NEW-5</v>
       </c>
       <c r="B2" t="str">
         <v>{{LABEL_ID}}</v>
@@ -715,7 +715,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>NEW-2</v>
+        <v>NEW-6</v>
       </c>
       <c r="B3" t="str">
         <v>{{LABEL_ID}}</v>
